--- a/Pruebas calificadas/COLEGIO-LUCILA-RUBIO-DE-LAVERDE-(IED)-PRUEBA-DIAGNÓSTICA-501_e5406098-REV_Ajustado_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-LUCILA-RUBIO-DE-LAVERDE-(IED)-PRUEBA-DIAGNÓSTICA-501_e5406098-REV_Ajustado_CALIFICADO.xlsx
@@ -807,8 +807,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -1048,8 +1056,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -1289,8 +1305,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -1530,8 +1554,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -1771,8 +1803,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -2012,8 +2052,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -2253,8 +2301,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -2494,8 +2550,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -2735,8 +2799,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -2976,8 +3048,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -3213,8 +3293,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -3454,8 +3542,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -3695,8 +3791,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -3936,8 +4040,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -4177,8 +4289,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -4418,8 +4538,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -4659,8 +4787,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -4900,8 +5036,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="2" t="inlineStr"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -5137,8 +5281,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-      <c r="B20" s="2" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -5378,8 +5530,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="2" t="inlineStr"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -5615,8 +5775,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="2" t="inlineStr"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -5856,8 +6024,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
-      <c r="B23" s="2" t="inlineStr"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -6097,8 +6273,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="2" t="inlineStr"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -6338,8 +6522,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-      <c r="B25" s="2" t="inlineStr"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -6579,8 +6771,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-      <c r="B26" s="2" t="inlineStr"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -6820,8 +7020,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
-      <c r="B27" s="2" t="inlineStr"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -7061,8 +7269,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-      <c r="B28" s="2" t="inlineStr"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -7298,8 +7514,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
-      <c r="B29" s="2" t="inlineStr"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -7539,8 +7763,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
-      <c r="B30" s="2" t="inlineStr"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -7772,8 +8004,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
-      <c r="B31" s="2" t="inlineStr"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -8013,8 +8253,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="inlineStr"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -8254,8 +8502,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-      <c r="B33" s="2" t="inlineStr"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -8495,8 +8751,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr"/>
-      <c r="B34" s="2" t="inlineStr"/>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -8736,8 +9000,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
-      <c r="B35" s="2" t="inlineStr"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -8977,8 +9249,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr"/>
-      <c r="B36" s="2" t="inlineStr"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -9202,8 +9482,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
-      <c r="B37" s="2" t="inlineStr"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -9443,8 +9731,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
-      <c r="B38" s="2" t="inlineStr"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -9680,8 +9976,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="2" t="inlineStr"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -9921,8 +10225,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="2" t="inlineStr"/>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -10162,8 +10474,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr"/>
-      <c r="B41" s="2" t="inlineStr"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -10403,8 +10723,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr"/>
-      <c r="B42" s="2" t="inlineStr"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -10644,8 +10972,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr"/>
-      <c r="B43" s="2" t="inlineStr"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -10885,8 +11221,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-      <c r="B44" s="2" t="inlineStr"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -11126,8 +11470,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
-      <c r="B45" s="2" t="inlineStr"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -11367,8 +11719,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
-      <c r="B46" s="2" t="inlineStr"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -11608,8 +11968,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr"/>
-      <c r="B47" s="2" t="inlineStr"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -11849,8 +12217,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr"/>
-      <c r="B48" s="2" t="inlineStr"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -12090,8 +12466,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr"/>
-      <c r="B49" s="2" t="inlineStr"/>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -12327,8 +12711,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr"/>
-      <c r="B50" s="2" t="inlineStr"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -12568,8 +12960,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr"/>
-      <c r="B51" s="2" t="inlineStr"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -12809,8 +13209,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr"/>
-      <c r="B52" s="2" t="inlineStr"/>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -13046,8 +13454,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr"/>
-      <c r="B53" s="2" t="inlineStr"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -13287,8 +13703,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr"/>
-      <c r="B54" s="2" t="inlineStr"/>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -13524,8 +13948,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr"/>
-      <c r="B55" s="2" t="inlineStr"/>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -13765,8 +14197,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr"/>
-      <c r="B56" s="2" t="inlineStr"/>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -14002,8 +14442,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr"/>
-      <c r="B57" s="2" t="inlineStr"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -14243,8 +14691,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr"/>
-      <c r="B58" s="2" t="inlineStr"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -14484,8 +14940,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr"/>
-      <c r="B59" s="2" t="inlineStr"/>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -14725,8 +15189,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr"/>
-      <c r="B60" s="2" t="inlineStr"/>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -14962,8 +15434,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr"/>
-      <c r="B61" s="2" t="inlineStr"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -15203,8 +15683,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr"/>
-      <c r="B62" s="2" t="inlineStr"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -15440,8 +15928,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr"/>
-      <c r="B63" s="2" t="inlineStr"/>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -15681,8 +16177,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr"/>
-      <c r="B64" s="2" t="inlineStr"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -15922,8 +16426,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr"/>
-      <c r="B65" s="2" t="inlineStr"/>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -16163,8 +16675,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr"/>
-      <c r="B66" s="2" t="inlineStr"/>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -16404,8 +16924,16 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -16617,8 +17145,16 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr"/>
-      <c r="B68" s="2" t="inlineStr"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -16858,8 +17394,16 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr"/>
-      <c r="B69" s="2" t="inlineStr"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -17099,8 +17643,16 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr"/>
-      <c r="B70" s="2" t="inlineStr"/>
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -17340,8 +17892,16 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr"/>
-      <c r="B71" s="2" t="inlineStr"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -17581,8 +18141,16 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr"/>
-      <c r="B72" s="2" t="inlineStr"/>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
@@ -17822,8 +18390,16 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr"/>
-      <c r="B73" s="2" t="inlineStr"/>
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>111001801071</t>
+        </is>
+      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>COLEGIO LUCILA RUBIO DE LAVERDE (IED)</t>
